--- a/総合テスト/シナリオテスト/総合テスト_シナリオテスト.xlsx
+++ b/総合テスト/シナリオテスト/総合テスト_シナリオテスト.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avantg-my.sharepoint.com/personal/shogo_maeda_avantcorp_com/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="91" documentId="8_{5E30CF43-FF73-4F37-A41D-046228F12B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{82BFC2B1-AF17-4F40-B485-2FE0497B0BAE}"/>
+  <xr:revisionPtr revIDLastSave="158" documentId="8_{5E30CF43-FF73-4F37-A41D-046228F12B0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB368C75-4B28-4D68-9842-CAD1F96990CB}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="5" xr2:uid="{B9F81D34-8753-435A-8C3F-2E5D22C8DBD0}"/>
+    <workbookView minimized="1" xWindow="5140" yWindow="3450" windowWidth="14400" windowHeight="8170" xr2:uid="{B9F81D34-8753-435A-8C3F-2E5D22C8DBD0}"/>
   </bookViews>
   <sheets>
-    <sheet name="5-1" sheetId="1" r:id="rId1"/>
-    <sheet name="5-2" sheetId="2" r:id="rId2"/>
-    <sheet name="5-3" sheetId="3" r:id="rId3"/>
-    <sheet name="5-4" sheetId="4" r:id="rId4"/>
-    <sheet name="5-5" sheetId="5" r:id="rId5"/>
-    <sheet name="5-6" sheetId="6" r:id="rId6"/>
-    <sheet name="5-7" sheetId="7" r:id="rId7"/>
+    <sheet name="ST-SC-001" sheetId="1" r:id="rId1"/>
+    <sheet name="ST-SC-002" sheetId="2" r:id="rId2"/>
+    <sheet name="ST-SC-003" sheetId="3" r:id="rId3"/>
+    <sheet name="ST-SC-004" sheetId="4" r:id="rId4"/>
+    <sheet name="ST-SC-005" sheetId="5" r:id="rId5"/>
+    <sheet name="ST-SC-006" sheetId="6" r:id="rId6"/>
+    <sheet name="ST-SC-007" sheetId="7" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,13 +44,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="19">
   <si>
-    <t>ログイン画面</t>
-    <rPh sb="4" eb="6">
-      <t>ガメン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>詳細画面及びカート追加処理</t>
     <rPh sb="0" eb="2">
       <t>ショウサイ</t>
@@ -201,6 +194,40 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>お客様情報入力画面における電話番号入力欄に文字を追加（エラーメッセージ表示確認）</t>
+    <rPh sb="1" eb="3">
+      <t>キャクサマ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ジョウホウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>デンワ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>バンゴウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>ニュウリョク</t>
+    </rPh>
+    <rPh sb="19" eb="20">
+      <t>ラン</t>
+    </rPh>
+    <rPh sb="21" eb="23">
+      <t>モジ</t>
+    </rPh>
+    <rPh sb="24" eb="26">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>電話番号入力欄に異常な数の数字を入力（エラーメッセージ表示確認）</t>
     <rPh sb="0" eb="4">
       <t>デンワバンゴウ</t>
@@ -232,61 +259,21 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>お客様情報入力画面における電話番号入力欄に文字を追加（エラーメッセージ表示確認）</t>
-    <rPh sb="1" eb="3">
-      <t>キャクサマ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
+    <t>「OK」ボタンを押した後、カート情報の維持確認</t>
+    <rPh sb="8" eb="9">
+      <t>オ</t>
+    </rPh>
+    <rPh sb="11" eb="12">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="16" eb="18">
       <t>ジョウホウ</t>
     </rPh>
-    <rPh sb="5" eb="7">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ガメン</t>
-    </rPh>
-    <rPh sb="13" eb="15">
-      <t>デンワ</t>
-    </rPh>
-    <rPh sb="15" eb="17">
-      <t>バンゴウ</t>
-    </rPh>
-    <rPh sb="17" eb="19">
-      <t>ニュウリョク</t>
-    </rPh>
-    <rPh sb="19" eb="20">
-      <t>ラン</t>
+    <rPh sb="19" eb="21">
+      <t>イジ</t>
     </rPh>
     <rPh sb="21" eb="23">
-      <t>モジ</t>
-    </rPh>
-    <rPh sb="24" eb="26">
-      <t>ツイカ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>カートに商品を追加した後にDBで在庫を０にして注文内容確認画面へ</t>
-    <rPh sb="4" eb="6">
-      <t>ショウヒン</t>
-    </rPh>
-    <rPh sb="7" eb="9">
-      <t>ツイカ</t>
-    </rPh>
-    <rPh sb="11" eb="12">
-      <t>ノチ</t>
-    </rPh>
-    <rPh sb="16" eb="18">
-      <t>ザイコ</t>
-    </rPh>
-    <rPh sb="23" eb="25">
-      <t>チュウモン</t>
-    </rPh>
-    <rPh sb="25" eb="29">
-      <t>ナイヨウカクニン</t>
-    </rPh>
-    <rPh sb="29" eb="31">
-      <t>ガメン</t>
+      <t>カクニン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -320,21 +307,43 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>「OK」ボタンを押した後、カート情報の維持確認</t>
-    <rPh sb="8" eb="9">
-      <t>オ</t>
+    <t>ログイン後画面</t>
+    <rPh sb="4" eb="5">
+      <t>アト</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ガメン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カートに商品を追加した後にDBで在庫を０にして注文内容確認画面へ（未ログイン状態）</t>
+    <rPh sb="4" eb="6">
+      <t>ショウヒン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ツイカ</t>
     </rPh>
     <rPh sb="11" eb="12">
-      <t>アト</t>
+      <t>ノチ</t>
     </rPh>
     <rPh sb="16" eb="18">
-      <t>ジョウホウ</t>
-    </rPh>
-    <rPh sb="19" eb="21">
-      <t>イジ</t>
-    </rPh>
-    <rPh sb="21" eb="23">
-      <t>カクニン</t>
+      <t>ザイコ</t>
+    </rPh>
+    <rPh sb="23" eb="25">
+      <t>チュウモン</t>
+    </rPh>
+    <rPh sb="25" eb="29">
+      <t>ナイヨウカクニン</t>
+    </rPh>
+    <rPh sb="29" eb="31">
+      <t>ガメン</t>
+    </rPh>
+    <rPh sb="33" eb="34">
+      <t>ミ</t>
+    </rPh>
+    <rPh sb="38" eb="40">
+      <t>ジョウタイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -408,39 +417,45 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>189583</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1ADACB59-BDA5-55A6-E580-E7D932DB6656}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="660401" y="228600"/>
-          <a:ext cx="8114382" cy="4324350"/>
+      <xdr:rowOff>24989</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="図 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0AA63378-061D-562F-6D46-54EE37EB52E0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="228600"/>
+          <a:ext cx="7772400" cy="4139789"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -457,26 +472,32 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>578321</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>197095</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D07EE74-5A82-F5CA-578C-1FDABC69F18E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>164281</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="図 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8DBB6732-1664-DC4F-A470-2973901AA151}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -484,271 +505,307 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="660400" y="5029200"/>
-          <a:ext cx="9163521" cy="4769095"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>628650</xdr:colOff>
+          <a:ext cx="7772400" cy="4050481"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>45</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>146466</xdr:colOff>
-      <xdr:row>67</xdr:row>
-      <xdr:rowOff>139960</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{15D550C6-74B8-F70F-C3B2-7320556D68FC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="628650" y="10388600"/>
-          <a:ext cx="8103016" cy="5067560"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>60195</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="図 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1B2B7AC-D82A-6CA3-B1AB-932F8754C81A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="10287000"/>
+          <a:ext cx="7772400" cy="4860795"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>71</xdr:row>
-      <xdr:rowOff>12700</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>235368</xdr:colOff>
-      <xdr:row>92</xdr:row>
-      <xdr:rowOff>152654</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8129AE6D-3D6B-895D-46E8-85315024A5D4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="679450" y="16243300"/>
-          <a:ext cx="8141118" cy="4940554"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>6350</xdr:colOff>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>91</xdr:row>
+      <xdr:rowOff>147173</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="図 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C1B04686-F982-5118-9642-18B9B6E84DA3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="16230600"/>
+          <a:ext cx="7772400" cy="4719173"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>95</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>70159</xdr:colOff>
-      <xdr:row>115</xdr:row>
-      <xdr:rowOff>70083</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BD91635C-4245-8D97-A112-275D2AA6A9AC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="666750" y="21818600"/>
-          <a:ext cx="6007409" cy="4540483"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>628650</xdr:colOff>
+      <xdr:colOff>450850</xdr:colOff>
+      <xdr:row>116</xdr:row>
+      <xdr:rowOff>27311</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="19" name="図 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ED80FA38-5123-EEBF-FF53-549F3E433EE0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="21717000"/>
+          <a:ext cx="6394450" cy="4827911"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>118</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>578255</xdr:colOff>
-      <xdr:row>137</xdr:row>
-      <xdr:rowOff>12922</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{47831D29-91A2-C9BD-C298-30EFA34C161F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="628650" y="27019250"/>
-          <a:ext cx="7874405" cy="4311872"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>44450</xdr:colOff>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>136</xdr:row>
+      <xdr:rowOff>147483</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="図 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6E02CEF2-B67A-B084-7260-BD5F5BEDB8AA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="26974800"/>
+          <a:ext cx="7772400" cy="4262283"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>140</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>552849</xdr:colOff>
+      <xdr:colOff>508000</xdr:colOff>
       <xdr:row>159</xdr:row>
-      <xdr:rowOff>190730</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="図 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C5C49662-61FF-E2E6-68B1-3956F6DF3D9C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="704850" y="32054800"/>
-          <a:ext cx="7772799" cy="4483330"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>622300</xdr:colOff>
-      <xdr:row>162</xdr:row>
-      <xdr:rowOff>222250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>229089</xdr:colOff>
-      <xdr:row>180</xdr:row>
-      <xdr:rowOff>133557</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="9" name="図 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4AA10FB0-DDC9-C64A-323C-86816CAB8CF1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="622300" y="37255450"/>
-          <a:ext cx="9512789" cy="4026107"/>
+      <xdr:rowOff>146050</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="23" name="図 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E5172C2E-3D34-5406-B78D-CD3D80202AF8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="32004000"/>
+          <a:ext cx="7772400" cy="4489450"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>164</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>178</xdr:row>
+      <xdr:rowOff>92110</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="25" name="図 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AE73A32F-B9C8-5BC4-B5D7-C546A14F54C9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="37490400"/>
+          <a:ext cx="7772400" cy="3292510"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -770,26 +827,32 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>159165</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>82801</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67083650-8C6C-5508-346A-919E83ADF0FC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>123188</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A06B0BDE-F641-482B-DEDE-2371E983C96F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -797,139 +860,157 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="660400" y="457200"/>
-          <a:ext cx="8083965" cy="4883401"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>647700</xdr:colOff>
+          <a:ext cx="7772400" cy="4695188"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>597305</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>101832</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{46190A9B-29CF-5D52-2925-8CB94D8787DC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="647700" y="5873750"/>
-          <a:ext cx="7874405" cy="4515082"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>76200</xdr:colOff>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>109602</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8BBB376F-A9D2-D226-A742-33D83E737B3B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="5715000"/>
+          <a:ext cx="7772400" cy="4453002"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>101600</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>470158</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>203440</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{87F96826-46F3-5F71-1003-8774B3AA6A59}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="736600" y="11074400"/>
-          <a:ext cx="5016758" cy="4673840"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>107951</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>222507</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9674E0F5-089C-CA9F-7670-06B260B6A87C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660401" y="10972800"/>
+          <a:ext cx="5391150" cy="5023107"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>71</xdr:row>
-      <xdr:rowOff>184150</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>514743</xdr:colOff>
-      <xdr:row>90</xdr:row>
-      <xdr:rowOff>108169</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="図 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6448C428-C086-87EA-763E-8947ECA34399}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="793750" y="16414750"/>
-          <a:ext cx="7645793" cy="4267419"/>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>89</xdr:row>
+      <xdr:rowOff>223283</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="図 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{166A6846-75E5-1FEB-877C-A62F232CCC76}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="16230600"/>
+          <a:ext cx="7772400" cy="4338083"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -943,37 +1024,43 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>93</xdr:row>
-      <xdr:rowOff>184150</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>279788</xdr:colOff>
-      <xdr:row>112</xdr:row>
-      <xdr:rowOff>12914</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E985557E-41F9-BDD9-E751-1B8E163009D9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="660400" y="21443950"/>
-          <a:ext cx="7544188" cy="4172164"/>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>111</xdr:row>
+      <xdr:rowOff>183572</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="図 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{693902BA-2948-7C23-9B30-DC7051F2CEFB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="21259800"/>
+          <a:ext cx="7772400" cy="4298372"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -990,39 +1077,45 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>82550</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>489378</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>159000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3A717397-CEC5-1D93-FBFD-6211808D7584}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="742950" y="781050"/>
-          <a:ext cx="8331628" cy="4864350"/>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>200373</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{09620C83-5B21-42FC-E688-5FEA667BB5BB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="685800"/>
+          <a:ext cx="7772400" cy="4543773"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1039,127 +1132,145 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>50800</xdr:colOff>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>107950</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>405</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>51032</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{551FCB37-57D8-4DF3-813B-2BDFDE8351E2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="711200" y="565150"/>
-          <a:ext cx="7874405" cy="4515082"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>647700</xdr:colOff>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>186472</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="図 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{705EF3C8-6026-9252-A9EE-C769EC341451}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="457200"/>
+          <a:ext cx="7772400" cy="3844072"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>381258</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>139940</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A6394B96-F35C-4BD5-9CC7-E3B4323AFEF2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="647700" y="5753100"/>
-          <a:ext cx="5016758" cy="4673840"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>603250</xdr:colOff>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>19051</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>139677</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="図 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{575C006F-99DD-D1A5-CD00-AB8073619C60}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660401" y="5715001"/>
+          <a:ext cx="5302250" cy="4940276"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>48</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>470300</xdr:colOff>
+      <xdr:colOff>508000</xdr:colOff>
       <xdr:row>64</xdr:row>
-      <xdr:rowOff>216095</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65F495B8-781C-EA5B-97DF-7D3F6DC77D36}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="603250" y="11049000"/>
-          <a:ext cx="7791850" cy="3797495"/>
+      <xdr:rowOff>136749</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="図 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44B6A237-FA0C-D0E7-EF0D-0B6E8D620860}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="10972800"/>
+          <a:ext cx="7772400" cy="3794349"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1181,78 +1292,90 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>330200</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>181121</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DF88CEBD-7D08-D2E9-D23C-69FB56E9EF98}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="685800"/>
+          <a:ext cx="5613400" cy="4295921"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>305189</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>82848</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{737D60EF-0A17-349D-6B0E-0E9D96085E82}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="660400" y="685800"/>
-          <a:ext cx="7569589" cy="5797848"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>6350</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>184150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>514749</xdr:colOff>
+      <xdr:colOff>508000</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>222546</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E38F0C73-5242-1F2F-5D86-12180B8F36D5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="666750" y="7727950"/>
-          <a:ext cx="7772799" cy="5753396"/>
+      <xdr:rowOff>38099</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D50541FE-A784-C675-B7FE-4DABFB45CF51}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="7543800"/>
+          <a:ext cx="7772400" cy="5753099"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1268,40 +1391,46 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>635000</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>432231</xdr:colOff>
-      <xdr:row>30</xdr:row>
-      <xdr:rowOff>133671</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CE8D3F7-5BB8-A7E8-98D2-2B2C35A878E6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="635000" y="736600"/>
-          <a:ext cx="8382431" cy="6255071"/>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>90747</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDF677C0-0797-E797-C2E8-1A0803D5B55A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="660400" y="685800"/>
+          <a:ext cx="7772400" cy="5805747"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1318,26 +1447,32 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>502219</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>139977</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE78D8AF-5AB3-AF49-AA2B-D82E7EE8F4D4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>137186</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A5C7E13B-8AC0-5E27-8E68-7A1D1C945883}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1345,7 +1480,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="660400" y="7543800"/>
-          <a:ext cx="11068619" cy="5397777"/>
+          <a:ext cx="7772400" cy="3794786"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1367,26 +1502,32 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>82962</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>197083</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DD82A628-C9AF-C714-916C-EF37F57B418E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+      <xdr:rowOff>69794</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="図 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98C16146-8A0F-5C6C-6C31-3C62EB27B8E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1394,7 +1535,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="660400" y="457200"/>
-          <a:ext cx="8007762" cy="4540483"/>
+          <a:ext cx="7772400" cy="4413194"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1411,26 +1552,32 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>171866</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>44758</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1AEBE60D-3B0C-28F8-3E66-590AA2C6F395}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>33528</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="図 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1F498C9D-D5A5-4DB9-ED58-F08D034B702F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -1438,7 +1585,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="660400" y="5715000"/>
-          <a:ext cx="8096666" cy="5988358"/>
+          <a:ext cx="7772400" cy="5748528"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1772,42 +1919,42 @@
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B1" t="s">
-        <v>0</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B22" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B45" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B71" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="95" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B95" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="118" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B118" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B140" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="163" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B163" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1824,27 +1971,27 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="71" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B71" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="93" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B93" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1861,7 +2008,7 @@
   <sheetData>
     <row r="3" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1878,17 +2025,17 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B48" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -1905,7 +2052,7 @@
   <sheetData>
     <row r="3" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.55000000000000004">
@@ -1927,12 +2074,12 @@
   <sheetData>
     <row r="3" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="33" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B33" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -1949,12 +2096,12 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.55000000000000004">
       <c r="B25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
